--- a/artfynd/A 56241-2022 artfynd.xlsx
+++ b/artfynd/A 56241-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56241-2022 artfynd.xlsx
+++ b/artfynd/A 56241-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6548,156 +6548,6 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>113141516</v>
-      </c>
-      <c r="B41" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Storberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>503268</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7007011</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Relativt gott om lunglav på minst 4 st. granar av olika dimensioner som står nära en gammal grov sälg med lunglav. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 56241-2022.</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Äldre luckig och flerskiktad grandominerad skog med inslag av tall och björk på frisk till frisk-fuktig mark. Terrängen är småkuperad och på flera ställen ligger stora block. I skogsbeståndet finns kolade stubbar som indikerar tidigare brand.</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Minst 4 st. granar.</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Minst 4 st. granar.</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
